--- a/Payment_REQ&RES_1 (1).xlsx
+++ b/Payment_REQ&RES_1 (1).xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Credit Card" sheetId="1" state="visible" r:id="rId2"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="120">
   <si>
     <t xml:space="preserve">PAYMENT TYPE</t>
   </si>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">https://payport.novalnet.de/v2/payment</t>
   </si>
   <si>
-    <t xml:space="preserve">testmode1</t>
+    <t xml:space="preserve">testmode0</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -181,7 +181,7 @@
                 (
                     [pan_hash] =&gt; l7v4djup1kzraf5q9hy8623ebc1784176215
                     [unique_id] =&gt; y9zh9q5fpar1vjdzk1np4ujd44v7nl
-                )C8
+                )
             [return_url] =&gt; http://wordpress6-test.projectfpm.che/checkout/order-received/260/?key=wc_order_85mypz3e6tdbb&amp;#038,wc-api=response_novalnet_cc&amp;#038,nn_return=52e28b7c63&amp;#038,order-id=260
         )
     [customer] =&gt; array
@@ -409,15 +409,93 @@
     <t xml:space="preserve">payment action authorize</t>
   </si>
   <si>
-    <t xml:space="preserve">$sheet-&gt;setCellValue('C4', '=array(...)');========================  request =============================
-arrayC8
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+array
 (
+    [custom] =&gt; array
+        (
+            [input1] =&gt; nn_shopnr
+            [input5] =&gt; nn_order_id
+            [inputval1] =&gt; 265
+            [inputval5] =&gt; 265
+            [nn_order_id] =&gt; 265
+            [nn_shopnr] =&gt; 265
+        )
+    [customer] =&gt; array
+        (
+            [billing] =&gt; array
+                (
+                    [city] =&gt; berlin
+                    [country_code] =&gt; de
+                    [house_no] =&gt; -
+                    [state] =&gt; berlin
+                    [street] =&gt; berlin
+                    [zip] =&gt; 66862
+                )
+            [customer_ip] =&gt; 192.168.2.90
+            [customer_no] =&gt; 1
+            [email] =&gt; madhu@gmail.com
+            [first_name] =&gt; test
+            [gender] =&gt; u
+            [last_name] =&gt; t
+            [tel] =&gt; 6746666687
+        )
     [merchant] =&gt; array
         (
-            [signature] =&gt; 7ibc7ob5,tujeh3gnbewjfihah,,nbobljbnmdli0poys,dou3hjvoym7mq44qf7cpn7pc
-            [tariff] =&gt; 10003
+            [project] =&gt; 6120
+            [vendor] =&gt; 4
+        )
+    [result] =&gt; array
+        (
+            [status] =&gt; success
+            [status_code] =&gt; 100
+            [status_text] =&gt; successful
+        )
+    [subscription] =&gt; array
+        (
+            [amount] =&gt; 1001
+            [currency] =&gt; eur
+            [next_cycle_date] =&gt; 2026-8-16 6:37:27
+            [payment_type] =&gt; creditcard
+            [status] =&gt; inactive
+            [subs_id] =&gt; 2804230
+            [tid] =&gt; 1.5416000020418E+016
         )
     [transaction] =&gt; array
+        (
+            [amount] =&gt; 1001
+            [authorization] =&gt; array
+                (
+                    [auto_action] =&gt; capture
+                    [expiry_date] =&gt; 2026-7-22
+                )
+            [currency] =&gt; eur
+            [date] =&gt; 2026-7-16 6:37:27
+            [order_no] =&gt; 265
+            [payment_data] =&gt; array
+                (
+                    [card_brand] =&gt; visa
+                    [card_expiry_month] =&gt; 12
+                    [card_expiry_year] =&gt; 2032
+                    [card_holder] =&gt; test t
+                    [card_number] =&gt; xxxxxxxxxxxx1091
+                    [cc_3d] =&gt; 1
+                    [last_four] =&gt; 1091
+                )
+            [payment_type] =&gt; creditcard
+            [status] =&gt; on_hold
+            [status_code] =&gt; 98
+            [test_mode] =&gt; 1
+            [tid] =&gt; 1.5416000020418E+016
+            [txn_secret] =&gt; b588c24c34edde8ceafa3975ac85b9e6
+        )
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [transaction] =&gt; array
         (
             [payment_type] =&gt; creditcardb3
             [test_mode] =&gt; 1
@@ -435,139 +513,6 @@
                 )C4
             [return_url] =&gt; http://wordpress6-test.projectfpm.che/checkout/order-received/265/?key=wc_order_q8mfct7rbutll&amp;#038,wc-api=response_novalnet_cc&amp;#038,nn_return=52e28b7c63&amp;#038,order-id=265
         )
-    [customer] =&gt; arrayB7
-        (
-            [first_name] =&gt; test
-            [last_name] =&gt; t
-            [email] =&gt; madhu@gmail.com
-            [tel] =&gt; 6746666687
-            [customer_ip] =&gt; 192.168.2.90
-            [customer_no] =&gt; 1
-            [billing] =&gt; arrayd4
-                (
-                    [street] =&gt; berlin 
-                    [city] =&gt; berlin
-                    [zip] =&gt; 66862
-                    [country_code] =&gt; de
-                    [state] =&gt; berlin
-                )
-            [shipping] =&gt; array
-                (
-                    [same_as_billing] =&gt; 1
-                )
-        )
-    [custom] =&gt; array
-        (
-            [lang] =&gt; en
-            [input5] =&gt; nn_order_id
-            [inputval5] =&gt; 265
-            [input1] =&gt; nn_shopnr
-            [inputval1] =&gt; 265
-        )
-)C4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-array
-(
-    [custom] =&gt; array
-        (
-            [input1] =&gt; nn_shopnr
-            [input5] =&gt; nn_order_id
-            [inputval1] =&gt; 265
-            [inputval5] =&gt; 265
-            [nn_order_id] =&gt; 265
-            [nn_shopnr] =&gt; 265
-        )
-    [customer] =&gt; array
-        (
-            [billing] =&gt; array
-                (
-                    [city] =&gt; berlin
-                    [country_code] =&gt; de
-                    [house_no] =&gt; -
-                    [state] =&gt; berlin
-                    [street] =&gt; berlin
-                    [zip] =&gt; 66862
-                )
-            [customer_ip] =&gt; 192.168.2.90
-            [customer_no] =&gt; 1
-            [email] =&gt; madhu@gmail.com
-            [first_name] =&gt; test
-            [gender] =&gt; u
-            [last_name] =&gt; t
-            [tel] =&gt; 6746666687
-        )
-    [merchant] =&gt; array
-        (
-            [project] =&gt; 6120
-            [vendor] =&gt; 4
-        )
-    [result] =&gt; array
-        (
-            [status] =&gt; success
-            [status_code] =&gt; 100
-            [status_text] =&gt; successful
-        )
-    [subscription] =&gt; array
-        (
-            [amount] =&gt; 1001
-            [currency] =&gt; eur
-            [next_cycle_date] =&gt; 2026-8-16 6:37:27
-            [payment_type] =&gt; creditcard
-            [status] =&gt; inactive
-            [subs_id] =&gt; 2804230
-            [tid] =&gt; 1.5416000020418E+016
-        )
-    [transaction] =&gt; array
-        (
-            [amount] =&gt; 1001
-            [authorization] =&gt; array
-                (
-                    [auto_action] =&gt; capture
-                    [expiry_date] =&gt; 2026-7-22
-                )
-            [currency] =&gt; eur
-            [date] =&gt; 2026-7-16 6:37:27
-            [order_no] =&gt; 265
-            [payment_data] =&gt; array
-                (
-                    [card_brand] =&gt; visa
-                    [card_expiry_month] =&gt; 12
-                    [card_expiry_year] =&gt; 2032
-                    [card_holder] =&gt; test t
-                    [card_number] =&gt; xxxxxxxxxxxx1091
-                    [cc_3d] =&gt; 1
-                    [last_four] =&gt; 1091
-                )
-            [payment_type] =&gt; creditcard
-            [status] =&gt; on_hold
-            [status_code] =&gt; 98
-            [test_mode] =&gt; 1
-            [tid] =&gt; 1.5416000020418E+016
-            [txn_secret] =&gt; b588c24c34edde8ceafa3975ac85b9e6
-        )
-)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> [transaction] =&gt; array
-        (
-            [payment_type] =&gt; creditcardb3
-            [test_mode] =&gt; 1
-            [amount] =&gt; 1300
-            [currency] =&gt; eur
-            [order_no] =&gt; 265
-            [system_name] =&gt; wordpress-woocommerce
-            [system_version] =&gt; 70.1-10.80.1-nn12.10.4
-            [system_url] =&gt; http://wordpress6-test.projectfpm.che
-            [system_ip] =&gt; 192.168.2.5
-            [payment_data] =&gt; array
-                (
-                    [pan_hash] =&gt; izmsd2le0xruho1gwba87f69354c1784176645
-                    [unique_id] =&gt; mbmxwgs1rnonhuerex0elz2ndsmnzi
-                )C4
-            [return_url] =&gt; http://wordpress6-test.projectfpm.che/checkout/order-received/265/?key=wc_order_q8mfct7rbutll&amp;#038,wc-api=response_novalnet_cc&amp;#038,nn_return=52e28b7c63&amp;#038,order-id=265
-        )
     [customer] =&gt; array
         (
             [first_name] =&gt; test
@@ -1104,6 +1049,81 @@
 )</t>
   </si>
   <si>
+    <t xml:space="preserve">
+array
+(
+    [custom] =&gt; arraye8
+        (
+            [input5] =&gt; nn_order_id
+            [inputval5] =&gt; 269
+            [nn_order_id] =&gt; 269
+        )
+    [customer] =&gt; array
+        (
+            [billing] =&gt; array
+                (
+                    [city] =&gt; berlind8
+                    [company] =&gt; abc gmbh
+                    [country_code] =&gt; de
+                    [house_no] =&gt; -
+                    [state] =&gt; berlin
+                    [street] =&gt; berlin
+                    [zip] =&gt; 6b36862
+                )
+A3
+            [customer_ip] =&gt; 192.168.2.90
+            [customer_no] =&gt; 1
+            [email] =&gt; madhu@gmail.com
+            [first_name] =&gt; test
+            [gender] =&gt; u
+            [last_name] =&gt; t
+            [tel] =&gt; 6746666687
+        )
+    [result] =&gt; array
+        (
+            [status] =&gt; success
+            [status_code] =&gt; 100
+            [status_text] =&gt; successful
+        )
+    [subscription] =&gt; array
+        (
+            [amount] =&gt; 1001
+            [currency] =&gt; eur
+            [next_cycle_date] =&gt; 2026-8-16 6:42:15
+            [payment_type] =&gt; creditcard
+            [status] =&gt; pending
+            [subs_id] =&gt; 2804237
+            [tid] =&gt; 1.5416000020519E+016
+        )
+    [transaction] =&gt; array
+        (
+            [amount] =&gt; 1001
+            [authorization] =&gt; array
+                (
+                    [auto_action] =&gt; capture
+                    [expiry_date] =&gt; 2026-7-22
+                )
+            [currency] =&gt; eur
+            [date] =&gt; 2026-7-16 6:42:15
+            [order_no] =&gt; 269
+            [payment_data] =&gt; array
+                (
+                    [card_brand] =&gt; visa
+                    [card_expiry_month] =&gt; 12
+                    [card_expiry_year] =&gt; 2032
+                    [card_holder] =&gt; test t
+                    [card_number] =&gt; xxxxxxxxxxxx0000
+                    [last_four] =&gt; 0
+                )
+            [payment_type] =&gt; creditcard
+            [status] =&gt; on_hold
+            [status_code] =&gt; 98
+            [test_mode] =&gt; 1
+            [tid] =&gt; 1.5416000020519E+016
+        )
+)</t>
+  </si>
+  <si>
     <t xml:space="preserve">request:
     [transaction] =&gt; Array
         (
@@ -3331,7 +3351,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">test mode1</t>
+    <t xml:space="preserve">test mode0</t>
   </si>
   <si>
     <t xml:space="preserve"> ======================
@@ -4557,6 +4577,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">    </t>
     </r>
@@ -4566,6 +4587,7 @@
         <color rgb="FFC9211E"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">[cart_info] =&gt; Array
         (
@@ -4590,6 +4612,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)
     [transaction] =&gt; Array
@@ -4611,6 +4634,7 @@
         <color rgb="FFC9211E"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> [return_url] =&gt; http://wordpress6-test.projectfpm.che/checkout/order-received/299/?key=wc_order_LDs1d8gAQbCor&amp;#038;wc-api=response_novalnet_paypal&amp;#038;nn_return=52e28b7c63&amp;#038;order-id=299
 </t>
@@ -4620,6 +4644,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">        )</t>
     </r>
@@ -4630,6 +4655,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">  [merchant] =&gt; Array
         (
@@ -4661,6 +4687,7 @@
         <color rgb="FF800080"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> [payment_data] =&gt; Array
                 (
@@ -4675,6 +4702,7 @@
         <color rgb="FFC9211E"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">            [payment_type] =&gt; PAYPAL
         </t>
@@ -4685,6 +4713,7 @@
         <color rgb="FF800080"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">    [status] =&gt; ON_HOLD
             [status_code] =&gt; 85
@@ -4696,6 +4725,7 @@
         <color rgb="FFC9211E"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">            [test_mode] =&gt; 1
             [tid] =&gt; 15416000037217703
@@ -4708,32 +4738,15 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">
 )</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF800080"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">https://payport.novalnet.de/v2/authorizeE4</t>
-    </r>
+    <t xml:space="preserve">
+https://payport.novalnet.de/v2/authorizeE4</t>
   </si>
   <si>
     <t xml:space="preserve">paypal capture</t>
@@ -4877,6 +4890,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> [transaction] =&gt; Array
         (
@@ -4897,6 +4911,7 @@
         <color rgb="FF800080"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> [return_url] =&gt; http://wordpress6-test.projectfpm.che/checkout/order-received/301/?key=wc_order_ITsUeytMjc4Mc&amp;#038;wc-api=response_novalnet_paypal&amp;#038;nn_return=52e28b7c63&amp;#038;order-id=301
 </t>
@@ -4906,6 +4921,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">        )</t>
     </r>
@@ -4916,6 +4932,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">  [transaction] =&gt; Array
         (
@@ -4936,6 +4953,7 @@
         <color rgb="FF800080"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">
             [payment_type] =&gt; PAYPAL
@@ -4948,6 +4966,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">            [test_mode] =&gt; 1
             [tid] =&gt; 15416000037902039
@@ -4964,7 +4983,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -5059,23 +5078,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFC9211E"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -5156,7 +5158,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -5249,12 +5251,8 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -5336,7 +5334,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultColWidth="243.01953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="243.54296875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="74.47"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="102.82"/>
@@ -5470,91 +5468,18 @@
       </c>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="684.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="895.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="0" t="e">
-        <f aca="false">====================  response ==========================================
-array
-(
-    [custom] =&gt; arraye8
-        (
-            [input5] =&gt; nn_order_id
-            [inputval5] =&gt; 269
-            [nn_order_id] =&gt; 269
-        )
-    [customer] =&gt; array
-        (
-            [billing] =&gt; array
-                (
-                    [city] =&gt; berlind8
-                    [company] =&gt; abc gmbh
-                    [country_code] =&gt; de
-                    [house_no] =&gt; -
-                    [state] =&gt; berlin
-                    [street] =&gt; berlin
-                    [zip] =&gt; 6b36862
-                )
-A3
-            [customer_ip] =&gt; 192.168.2.90
-            [customer_no] =&gt; 1
-            [email] =&gt; madhu@gmail.com
-            [first_name] =&gt; test
-            [gender] =&gt; u
-            [last_name] =&gt; t
-            [tel] =&gt; 6746666687
-        )
-    [result] =&gt; array
-        (
-            [status] =&gt; success
-            [status_code] =&gt; 100
-            [status_text] =&gt; successful
-        )
-    [subscription] =&gt; array
-        (
-            [amount] =&gt; 1001
-            [currency] =&gt; eur
-            [next_cycle_date] =&gt; 2026-8-16 6:42:15
-            [payment_type] =&gt; creditcard
-            [status] =&gt; pending
-            [subs_id] =&gt; 2804237
-            [tid] =&gt; 1.5416000020519E+016
-        )
-    [transaction] =&gt; array
-        (
-            [amount] =&gt; 1001
-            [authorization] =&gt; array
-                (
-                    [auto_action] =&gt; capture
-                    [expiry_date] =&gt; 2026-7-22
-                )
-            [currency] =&gt; eur
-            [date] =&gt; 2026-7-16 6:42:15
-            [order_no] =&gt; 269
-            [payment_data] =&gt; array
-                (
-                    [card_brand] =&gt; visa
-                    [card_expiry_month] =&gt; 12
-                    [card_expiry_year] =&gt; 2032
-                    [card_holder] =&gt; test t
-                    [card_number] =&gt; xxxxxxxxxxxx0000
-                    [last_four] =&gt; 0
-                )
-            [payment_type] =&gt; creditcard
-            [status] =&gt; on_hold
-            [status_code] =&gt; 98
-            [test_mode] =&gt; 1
-            [tid] =&gt; 1.5416000020519E+016
-        )
-)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" s="11"/>
     </row>
@@ -5579,7 +5504,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="21.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="113.11"/>
@@ -5600,7 +5525,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>3</v>
@@ -5611,19 +5536,19 @@
     </row>
     <row r="2" customFormat="false" ht="738.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F2" s="14" t="s">
         <v>9</v>
@@ -5631,66 +5556,66 @@
     </row>
     <row r="3" customFormat="false" ht="746.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="7"/>
     </row>
     <row r="4" customFormat="false" ht="807.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="729.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="799.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F6" s="3"/>
     </row>
@@ -5714,7 +5639,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G5"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="95.55"/>
@@ -5735,10 +5660,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>5</v>
@@ -5749,65 +5674,65 @@
     </row>
     <row r="2" customFormat="false" ht="828.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F2" s="18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="895.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="895.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="895.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -5830,7 +5755,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AH4"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.37"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="94.02"/>
@@ -5851,30 +5776,30 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="873.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="897" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F2" s="19" t="s">
         <v>9</v>
@@ -5883,36 +5808,36 @@
     </row>
     <row r="3" customFormat="false" ht="982.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="873.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -5935,7 +5860,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="193.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60.43"/>
@@ -5955,92 +5880,92 @@
         <v>2</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F1" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="705.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="817.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="873.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="D4" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>113</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="861.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="D5" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="D5" s="7" t="s">
         <v>118</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F4" r:id="rId1" display="https://payport.novalnet.de/v2/authorizeE4"/>
+    <hyperlink ref="F4" r:id="rId1" display="&#10;https://payport.novalnet.de/v2/authorizeE4"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
